--- a/IT22003928_Assignment1/IT22003928-Assignment01.xlsx
+++ b/IT22003928_Assignment1/IT22003928-Assignment01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IT22003928-Assignment1\IT22003928_Assignment1\IT22003928_Assignment1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EB82A31-B786-41EE-9129-B859A6CA2CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC136E5-624C-4D9B-BB97-943898D74A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{167F1541-5561-43F5-B552-96385F3CDF64}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" firstSheet="1" activeTab="1" xr2:uid="{167F1541-5561-43F5-B552-96385F3CDF64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -656,10 +656,10 @@
     <t>DepositType.xlsx</t>
   </si>
   <si>
+    <t>ReservationStatus.xlsx</t>
+  </si>
+  <si>
     <t>Excel file</t>
-  </si>
-  <si>
-    <t>ReservationStatus.csv</t>
   </si>
   <si>
     <t>JSON File</t>
@@ -2735,7 +2735,7 @@
         <v>204</v>
       </c>
       <c r="B90" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C90" t="s">
         <v>87</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="B94" t="s">
-        <v>82</v>
       </c>
       <c r="C94" t="s">
         <v>92</v>
